--- a/plans/strength_template.xlsx
+++ b/plans/strength_template.xlsx
@@ -690,7 +690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -860,15 +860,85 @@
       <c r="D15" s="7" t="inlineStr"/>
       <c r="E15" s="7" t="inlineStr"/>
     </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="7" t="inlineStr"/>
+      <c r="B16" s="7" t="inlineStr"/>
+      <c r="C16" s="7" t="inlineStr"/>
+      <c r="D16" s="7" t="inlineStr"/>
+      <c r="E16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="7" t="inlineStr"/>
+      <c r="B17" s="7" t="inlineStr"/>
+      <c r="C17" s="7" t="inlineStr"/>
+      <c r="D17" s="7" t="inlineStr"/>
+      <c r="E17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="7" t="inlineStr"/>
+      <c r="B18" s="7" t="inlineStr"/>
+      <c r="C18" s="7" t="inlineStr"/>
+      <c r="D18" s="7" t="inlineStr"/>
+      <c r="E18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="7" t="inlineStr"/>
+      <c r="B19" s="7" t="inlineStr"/>
+      <c r="C19" s="7" t="inlineStr"/>
+      <c r="D19" s="7" t="inlineStr"/>
+      <c r="E19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="7" t="inlineStr"/>
+      <c r="B20" s="7" t="inlineStr"/>
+      <c r="C20" s="7" t="inlineStr"/>
+      <c r="D20" s="7" t="inlineStr"/>
+      <c r="E20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="7" t="inlineStr"/>
+      <c r="B21" s="7" t="inlineStr"/>
+      <c r="C21" s="7" t="inlineStr"/>
+      <c r="D21" s="7" t="inlineStr"/>
+      <c r="E21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="7" t="inlineStr"/>
+      <c r="B22" s="7" t="inlineStr"/>
+      <c r="C22" s="7" t="inlineStr"/>
+      <c r="D22" s="7" t="inlineStr"/>
+      <c r="E22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="7" t="inlineStr"/>
+      <c r="B23" s="7" t="inlineStr"/>
+      <c r="C23" s="7" t="inlineStr"/>
+      <c r="D23" s="7" t="inlineStr"/>
+      <c r="E23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="7" t="inlineStr"/>
+      <c r="B24" s="7" t="inlineStr"/>
+      <c r="C24" s="7" t="inlineStr"/>
+      <c r="D24" s="7" t="inlineStr"/>
+      <c r="E24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="7" t="inlineStr"/>
+      <c r="B25" s="7" t="inlineStr"/>
+      <c r="C25" s="7" t="inlineStr"/>
+      <c r="D25" s="7" t="inlineStr"/>
+      <c r="E25" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="3">
     <dataValidation sqref="B1" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Неверный тип" error="Выбери тип из списка" type="list">
       <formula1>"Ноги + таз,Ноги,Верх + кор,Верх тела,Полное тело,Кардио,Растяжка,Йога,Вин Чун,Цигун,Отдых,Отдых + тест"</formula1>
     </dataValidation>
-    <dataValidation sqref="D4 D5 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D4 D5 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"да,"</formula1>
     </dataValidation>
-    <dataValidation sqref="E4 E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E4 E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"мин,сек,раз,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -882,7 +952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1049,15 +1119,85 @@
       <c r="D14" s="7" t="inlineStr"/>
       <c r="E14" s="7" t="inlineStr"/>
     </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="7" t="inlineStr"/>
+      <c r="B15" s="7" t="inlineStr"/>
+      <c r="C15" s="7" t="inlineStr"/>
+      <c r="D15" s="7" t="inlineStr"/>
+      <c r="E15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="7" t="inlineStr"/>
+      <c r="B16" s="7" t="inlineStr"/>
+      <c r="C16" s="7" t="inlineStr"/>
+      <c r="D16" s="7" t="inlineStr"/>
+      <c r="E16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="7" t="inlineStr"/>
+      <c r="B17" s="7" t="inlineStr"/>
+      <c r="C17" s="7" t="inlineStr"/>
+      <c r="D17" s="7" t="inlineStr"/>
+      <c r="E17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="7" t="inlineStr"/>
+      <c r="B18" s="7" t="inlineStr"/>
+      <c r="C18" s="7" t="inlineStr"/>
+      <c r="D18" s="7" t="inlineStr"/>
+      <c r="E18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="7" t="inlineStr"/>
+      <c r="B19" s="7" t="inlineStr"/>
+      <c r="C19" s="7" t="inlineStr"/>
+      <c r="D19" s="7" t="inlineStr"/>
+      <c r="E19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="7" t="inlineStr"/>
+      <c r="B20" s="7" t="inlineStr"/>
+      <c r="C20" s="7" t="inlineStr"/>
+      <c r="D20" s="7" t="inlineStr"/>
+      <c r="E20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="7" t="inlineStr"/>
+      <c r="B21" s="7" t="inlineStr"/>
+      <c r="C21" s="7" t="inlineStr"/>
+      <c r="D21" s="7" t="inlineStr"/>
+      <c r="E21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="7" t="inlineStr"/>
+      <c r="B22" s="7" t="inlineStr"/>
+      <c r="C22" s="7" t="inlineStr"/>
+      <c r="D22" s="7" t="inlineStr"/>
+      <c r="E22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="7" t="inlineStr"/>
+      <c r="B23" s="7" t="inlineStr"/>
+      <c r="C23" s="7" t="inlineStr"/>
+      <c r="D23" s="7" t="inlineStr"/>
+      <c r="E23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="7" t="inlineStr"/>
+      <c r="B24" s="7" t="inlineStr"/>
+      <c r="C24" s="7" t="inlineStr"/>
+      <c r="D24" s="7" t="inlineStr"/>
+      <c r="E24" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="3">
     <dataValidation sqref="B1" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Неверный тип" error="Выбери тип из списка" type="list">
       <formula1>"Ноги + таз,Ноги,Верх + кор,Верх тела,Полное тело,Кардио,Растяжка,Йога,Вин Чун,Цигун,Отдых,Отдых + тест"</formula1>
     </dataValidation>
-    <dataValidation sqref="D4 D5 D6 D7 D8 D9 D10 D11 D12 D13 D14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D4 D5 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"да,"</formula1>
     </dataValidation>
-    <dataValidation sqref="E4 E5 E6 E7 E8 E9 E10 E11 E12 E13 E14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E4 E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"мин,сек,раз,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1071,7 +1211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1222,15 +1362,85 @@
       <c r="D14" s="7" t="inlineStr"/>
       <c r="E14" s="7" t="inlineStr"/>
     </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="7" t="inlineStr"/>
+      <c r="B15" s="7" t="inlineStr"/>
+      <c r="C15" s="7" t="inlineStr"/>
+      <c r="D15" s="7" t="inlineStr"/>
+      <c r="E15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="7" t="inlineStr"/>
+      <c r="B16" s="7" t="inlineStr"/>
+      <c r="C16" s="7" t="inlineStr"/>
+      <c r="D16" s="7" t="inlineStr"/>
+      <c r="E16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="7" t="inlineStr"/>
+      <c r="B17" s="7" t="inlineStr"/>
+      <c r="C17" s="7" t="inlineStr"/>
+      <c r="D17" s="7" t="inlineStr"/>
+      <c r="E17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="7" t="inlineStr"/>
+      <c r="B18" s="7" t="inlineStr"/>
+      <c r="C18" s="7" t="inlineStr"/>
+      <c r="D18" s="7" t="inlineStr"/>
+      <c r="E18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="7" t="inlineStr"/>
+      <c r="B19" s="7" t="inlineStr"/>
+      <c r="C19" s="7" t="inlineStr"/>
+      <c r="D19" s="7" t="inlineStr"/>
+      <c r="E19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="7" t="inlineStr"/>
+      <c r="B20" s="7" t="inlineStr"/>
+      <c r="C20" s="7" t="inlineStr"/>
+      <c r="D20" s="7" t="inlineStr"/>
+      <c r="E20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="7" t="inlineStr"/>
+      <c r="B21" s="7" t="inlineStr"/>
+      <c r="C21" s="7" t="inlineStr"/>
+      <c r="D21" s="7" t="inlineStr"/>
+      <c r="E21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="7" t="inlineStr"/>
+      <c r="B22" s="7" t="inlineStr"/>
+      <c r="C22" s="7" t="inlineStr"/>
+      <c r="D22" s="7" t="inlineStr"/>
+      <c r="E22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="7" t="inlineStr"/>
+      <c r="B23" s="7" t="inlineStr"/>
+      <c r="C23" s="7" t="inlineStr"/>
+      <c r="D23" s="7" t="inlineStr"/>
+      <c r="E23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="7" t="inlineStr"/>
+      <c r="B24" s="7" t="inlineStr"/>
+      <c r="C24" s="7" t="inlineStr"/>
+      <c r="D24" s="7" t="inlineStr"/>
+      <c r="E24" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="3">
     <dataValidation sqref="B1" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Неверный тип" error="Выбери тип из списка" type="list">
       <formula1>"Ноги + таз,Ноги,Верх + кор,Верх тела,Полное тело,Кардио,Растяжка,Йога,Вин Чун,Цигун,Отдых,Отдых + тест"</formula1>
     </dataValidation>
-    <dataValidation sqref="D4 D5 D6 D7 D8 D9 D10 D11 D12 D13 D14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D4 D5 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"да,"</formula1>
     </dataValidation>
-    <dataValidation sqref="E4 E5 E6 E7 E8 E9 E10 E11 E12 E13 E14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E4 E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"мин,сек,раз,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1244,7 +1454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1376,15 +1586,85 @@
       <c r="D13" s="7" t="inlineStr"/>
       <c r="E13" s="7" t="inlineStr"/>
     </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="7" t="inlineStr"/>
+      <c r="B14" s="7" t="inlineStr"/>
+      <c r="C14" s="7" t="inlineStr"/>
+      <c r="D14" s="7" t="inlineStr"/>
+      <c r="E14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="7" t="inlineStr"/>
+      <c r="B15" s="7" t="inlineStr"/>
+      <c r="C15" s="7" t="inlineStr"/>
+      <c r="D15" s="7" t="inlineStr"/>
+      <c r="E15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="7" t="inlineStr"/>
+      <c r="B16" s="7" t="inlineStr"/>
+      <c r="C16" s="7" t="inlineStr"/>
+      <c r="D16" s="7" t="inlineStr"/>
+      <c r="E16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="7" t="inlineStr"/>
+      <c r="B17" s="7" t="inlineStr"/>
+      <c r="C17" s="7" t="inlineStr"/>
+      <c r="D17" s="7" t="inlineStr"/>
+      <c r="E17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="7" t="inlineStr"/>
+      <c r="B18" s="7" t="inlineStr"/>
+      <c r="C18" s="7" t="inlineStr"/>
+      <c r="D18" s="7" t="inlineStr"/>
+      <c r="E18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="7" t="inlineStr"/>
+      <c r="B19" s="7" t="inlineStr"/>
+      <c r="C19" s="7" t="inlineStr"/>
+      <c r="D19" s="7" t="inlineStr"/>
+      <c r="E19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="7" t="inlineStr"/>
+      <c r="B20" s="7" t="inlineStr"/>
+      <c r="C20" s="7" t="inlineStr"/>
+      <c r="D20" s="7" t="inlineStr"/>
+      <c r="E20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="7" t="inlineStr"/>
+      <c r="B21" s="7" t="inlineStr"/>
+      <c r="C21" s="7" t="inlineStr"/>
+      <c r="D21" s="7" t="inlineStr"/>
+      <c r="E21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="7" t="inlineStr"/>
+      <c r="B22" s="7" t="inlineStr"/>
+      <c r="C22" s="7" t="inlineStr"/>
+      <c r="D22" s="7" t="inlineStr"/>
+      <c r="E22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="7" t="inlineStr"/>
+      <c r="B23" s="7" t="inlineStr"/>
+      <c r="C23" s="7" t="inlineStr"/>
+      <c r="D23" s="7" t="inlineStr"/>
+      <c r="E23" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="3">
     <dataValidation sqref="B1" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Неверный тип" error="Выбери тип из списка" type="list">
       <formula1>"Ноги + таз,Ноги,Верх + кор,Верх тела,Полное тело,Кардио,Растяжка,Йога,Вин Чун,Цигун,Отдых,Отдых + тест"</formula1>
     </dataValidation>
-    <dataValidation sqref="D4 D5 D6 D7 D8 D9 D10 D11 D12 D13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D4 D5 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"да,"</formula1>
     </dataValidation>
-    <dataValidation sqref="E4 E5 E6 E7 E8 E9 E10 E11 E12 E13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E4 E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"мин,сек,раз,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1398,7 +1678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1549,15 +1829,85 @@
       <c r="D14" s="7" t="inlineStr"/>
       <c r="E14" s="7" t="inlineStr"/>
     </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="7" t="inlineStr"/>
+      <c r="B15" s="7" t="inlineStr"/>
+      <c r="C15" s="7" t="inlineStr"/>
+      <c r="D15" s="7" t="inlineStr"/>
+      <c r="E15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="7" t="inlineStr"/>
+      <c r="B16" s="7" t="inlineStr"/>
+      <c r="C16" s="7" t="inlineStr"/>
+      <c r="D16" s="7" t="inlineStr"/>
+      <c r="E16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="7" t="inlineStr"/>
+      <c r="B17" s="7" t="inlineStr"/>
+      <c r="C17" s="7" t="inlineStr"/>
+      <c r="D17" s="7" t="inlineStr"/>
+      <c r="E17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="7" t="inlineStr"/>
+      <c r="B18" s="7" t="inlineStr"/>
+      <c r="C18" s="7" t="inlineStr"/>
+      <c r="D18" s="7" t="inlineStr"/>
+      <c r="E18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="7" t="inlineStr"/>
+      <c r="B19" s="7" t="inlineStr"/>
+      <c r="C19" s="7" t="inlineStr"/>
+      <c r="D19" s="7" t="inlineStr"/>
+      <c r="E19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="7" t="inlineStr"/>
+      <c r="B20" s="7" t="inlineStr"/>
+      <c r="C20" s="7" t="inlineStr"/>
+      <c r="D20" s="7" t="inlineStr"/>
+      <c r="E20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="7" t="inlineStr"/>
+      <c r="B21" s="7" t="inlineStr"/>
+      <c r="C21" s="7" t="inlineStr"/>
+      <c r="D21" s="7" t="inlineStr"/>
+      <c r="E21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="7" t="inlineStr"/>
+      <c r="B22" s="7" t="inlineStr"/>
+      <c r="C22" s="7" t="inlineStr"/>
+      <c r="D22" s="7" t="inlineStr"/>
+      <c r="E22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="7" t="inlineStr"/>
+      <c r="B23" s="7" t="inlineStr"/>
+      <c r="C23" s="7" t="inlineStr"/>
+      <c r="D23" s="7" t="inlineStr"/>
+      <c r="E23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="7" t="inlineStr"/>
+      <c r="B24" s="7" t="inlineStr"/>
+      <c r="C24" s="7" t="inlineStr"/>
+      <c r="D24" s="7" t="inlineStr"/>
+      <c r="E24" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="3">
     <dataValidation sqref="B1" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Неверный тип" error="Выбери тип из списка" type="list">
       <formula1>"Ноги + таз,Ноги,Верх + кор,Верх тела,Полное тело,Кардио,Растяжка,Йога,Вин Чун,Цигун,Отдых,Отдых + тест"</formula1>
     </dataValidation>
-    <dataValidation sqref="D4 D5 D6 D7 D8 D9 D10 D11 D12 D13 D14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D4 D5 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"да,"</formula1>
     </dataValidation>
-    <dataValidation sqref="E4 E5 E6 E7 E8 E9 E10 E11 E12 E13 E14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E4 E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"мин,сек,раз,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1571,7 +1921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1738,15 +2088,85 @@
       <c r="D14" s="7" t="inlineStr"/>
       <c r="E14" s="7" t="inlineStr"/>
     </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="7" t="inlineStr"/>
+      <c r="B15" s="7" t="inlineStr"/>
+      <c r="C15" s="7" t="inlineStr"/>
+      <c r="D15" s="7" t="inlineStr"/>
+      <c r="E15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="7" t="inlineStr"/>
+      <c r="B16" s="7" t="inlineStr"/>
+      <c r="C16" s="7" t="inlineStr"/>
+      <c r="D16" s="7" t="inlineStr"/>
+      <c r="E16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="7" t="inlineStr"/>
+      <c r="B17" s="7" t="inlineStr"/>
+      <c r="C17" s="7" t="inlineStr"/>
+      <c r="D17" s="7" t="inlineStr"/>
+      <c r="E17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="7" t="inlineStr"/>
+      <c r="B18" s="7" t="inlineStr"/>
+      <c r="C18" s="7" t="inlineStr"/>
+      <c r="D18" s="7" t="inlineStr"/>
+      <c r="E18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="7" t="inlineStr"/>
+      <c r="B19" s="7" t="inlineStr"/>
+      <c r="C19" s="7" t="inlineStr"/>
+      <c r="D19" s="7" t="inlineStr"/>
+      <c r="E19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="7" t="inlineStr"/>
+      <c r="B20" s="7" t="inlineStr"/>
+      <c r="C20" s="7" t="inlineStr"/>
+      <c r="D20" s="7" t="inlineStr"/>
+      <c r="E20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="7" t="inlineStr"/>
+      <c r="B21" s="7" t="inlineStr"/>
+      <c r="C21" s="7" t="inlineStr"/>
+      <c r="D21" s="7" t="inlineStr"/>
+      <c r="E21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="7" t="inlineStr"/>
+      <c r="B22" s="7" t="inlineStr"/>
+      <c r="C22" s="7" t="inlineStr"/>
+      <c r="D22" s="7" t="inlineStr"/>
+      <c r="E22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="7" t="inlineStr"/>
+      <c r="B23" s="7" t="inlineStr"/>
+      <c r="C23" s="7" t="inlineStr"/>
+      <c r="D23" s="7" t="inlineStr"/>
+      <c r="E23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="7" t="inlineStr"/>
+      <c r="B24" s="7" t="inlineStr"/>
+      <c r="C24" s="7" t="inlineStr"/>
+      <c r="D24" s="7" t="inlineStr"/>
+      <c r="E24" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="3">
     <dataValidation sqref="B1" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Неверный тип" error="Выбери тип из списка" type="list">
       <formula1>"Ноги + таз,Ноги,Верх + кор,Верх тела,Полное тело,Кардио,Растяжка,Йога,Вин Чун,Цигун,Отдых,Отдых + тест"</formula1>
     </dataValidation>
-    <dataValidation sqref="D4 D5 D6 D7 D8 D9 D10 D11 D12 D13 D14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D4 D5 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"да,"</formula1>
     </dataValidation>
-    <dataValidation sqref="E4 E5 E6 E7 E8 E9 E10 E11 E12 E13 E14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E4 E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"мин,сек,раз,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1760,7 +2180,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1888,15 +2308,85 @@
       <c r="D13" s="7" t="inlineStr"/>
       <c r="E13" s="7" t="inlineStr"/>
     </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="7" t="inlineStr"/>
+      <c r="B14" s="7" t="inlineStr"/>
+      <c r="C14" s="7" t="inlineStr"/>
+      <c r="D14" s="7" t="inlineStr"/>
+      <c r="E14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="7" t="inlineStr"/>
+      <c r="B15" s="7" t="inlineStr"/>
+      <c r="C15" s="7" t="inlineStr"/>
+      <c r="D15" s="7" t="inlineStr"/>
+      <c r="E15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="7" t="inlineStr"/>
+      <c r="B16" s="7" t="inlineStr"/>
+      <c r="C16" s="7" t="inlineStr"/>
+      <c r="D16" s="7" t="inlineStr"/>
+      <c r="E16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="7" t="inlineStr"/>
+      <c r="B17" s="7" t="inlineStr"/>
+      <c r="C17" s="7" t="inlineStr"/>
+      <c r="D17" s="7" t="inlineStr"/>
+      <c r="E17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="7" t="inlineStr"/>
+      <c r="B18" s="7" t="inlineStr"/>
+      <c r="C18" s="7" t="inlineStr"/>
+      <c r="D18" s="7" t="inlineStr"/>
+      <c r="E18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="7" t="inlineStr"/>
+      <c r="B19" s="7" t="inlineStr"/>
+      <c r="C19" s="7" t="inlineStr"/>
+      <c r="D19" s="7" t="inlineStr"/>
+      <c r="E19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="7" t="inlineStr"/>
+      <c r="B20" s="7" t="inlineStr"/>
+      <c r="C20" s="7" t="inlineStr"/>
+      <c r="D20" s="7" t="inlineStr"/>
+      <c r="E20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="7" t="inlineStr"/>
+      <c r="B21" s="7" t="inlineStr"/>
+      <c r="C21" s="7" t="inlineStr"/>
+      <c r="D21" s="7" t="inlineStr"/>
+      <c r="E21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="7" t="inlineStr"/>
+      <c r="B22" s="7" t="inlineStr"/>
+      <c r="C22" s="7" t="inlineStr"/>
+      <c r="D22" s="7" t="inlineStr"/>
+      <c r="E22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="7" t="inlineStr"/>
+      <c r="B23" s="7" t="inlineStr"/>
+      <c r="C23" s="7" t="inlineStr"/>
+      <c r="D23" s="7" t="inlineStr"/>
+      <c r="E23" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="3">
     <dataValidation sqref="B1" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Неверный тип" error="Выбери тип из списка" type="list">
       <formula1>"Ноги + таз,Ноги,Верх + кор,Верх тела,Полное тело,Кардио,Растяжка,Йога,Вин Чун,Цигун,Отдых,Отдых + тест"</formula1>
     </dataValidation>
-    <dataValidation sqref="D4 D5 D6 D7 D8 D9 D10 D11 D12 D13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D4 D5 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"да,"</formula1>
     </dataValidation>
-    <dataValidation sqref="E4 E5 E6 E7 E8 E9 E10 E11 E12 E13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E4 E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"мин,сек,раз,"</formula1>
     </dataValidation>
   </dataValidations>
